--- a/Configs/GameConfig/Datas/global_config.xlsx
+++ b/Configs/GameConfig/Datas/global_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>##column##var</t>
   </si>
@@ -38,28 +38,16 @@
     <t>##comment</t>
   </si>
   <si>
-    <t>base_coin</t>
+    <t>energy_max</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>基础金币值</t>
-  </si>
-  <si>
-    <t>base_enery</t>
-  </si>
-  <si>
-    <t>基础体力值</t>
-  </si>
-  <si>
-    <t>energy_max</t>
-  </si>
-  <si>
     <t>体力上限</t>
   </si>
   <si>
-    <t>level_enery_consume</t>
+    <t>level_energy_consume</t>
   </si>
   <si>
     <t>推关消耗体力</t>
@@ -1057,8 +1045,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:V8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="25.5" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
@@ -1096,7 +1084,7 @@
       <c r="U1"/>
       <c r="V1"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" customFormat="1" spans="1:22">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1110,7 +1098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" customFormat="1" spans="1:22">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1118,65 +1106,65 @@
         <v>4</v>
       </c>
       <c r="C3" s="2">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:22">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
-        <v>150</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:22">
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
         <v>11</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1185,41 +1173,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="D8" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" t="s">
+      <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D8" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/global_config.xlsx
+++ b/Configs/GameConfig/Datas/global_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20580" windowHeight="15495"/>
+    <workbookView windowWidth="31335" windowHeight="15570"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>##column##var</t>
   </si>
@@ -80,16 +80,10 @@
     <t>广告倍率</t>
   </si>
   <si>
-    <t>daily_chest_energy_reward</t>
-  </si>
-  <si>
-    <t>common.IntRange</t>
-  </si>
-  <si>
-    <t>30,50</t>
-  </si>
-  <si>
-    <t>每日领取体力奖励范围</t>
+    <t>daily_checkin_reward_id</t>
+  </si>
+  <si>
+    <t>每日签到奖励id</t>
   </si>
 </sst>
 </file>
@@ -1173,13 +1167,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D8" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/global_config.xlsx
+++ b/Configs/GameConfig/Datas/global_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31335" windowHeight="15570"/>
+    <workbookView windowWidth="27195" windowHeight="16065"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>##column##var</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>每日签到奖励id</t>
+  </si>
+  <si>
+    <t>ad_reward_pack_ids</t>
+  </si>
+  <si>
+    <t>(list#sep=|),int</t>
+  </si>
+  <si>
+    <t>3001|3002</t>
+  </si>
+  <si>
+    <t>广告礼包ID</t>
   </si>
 </sst>
 </file>
@@ -712,7 +724,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -720,6 +732,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1039,8 +1052,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:V9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="25.5" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
@@ -1176,6 +1189,20 @@
         <v>18</v>
       </c>
     </row>
+    <row r="9" spans="1:22">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
